--- a/data/secondary2/secondary_quote_2026-07-23.xlsx
+++ b/data/secondary2/secondary_quote_2026-07-23.xlsx
@@ -13,42 +13,717 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="125">
-  <si>
-    <t>暂无数据</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="341">
+  <si>
+    <t>债券简称</t>
+  </si>
+  <si>
+    <t>债券代码</t>
+  </si>
+  <si>
+    <t>剩余期限</t>
+  </si>
+  <si>
+    <t>最新成交</t>
+  </si>
+  <si>
+    <t>开盘</t>
+  </si>
+  <si>
+    <t>最高</t>
+  </si>
+  <si>
+    <t>最低</t>
+  </si>
+  <si>
+    <t>平均成交</t>
+  </si>
+  <si>
+    <t>前收</t>
+  </si>
+  <si>
+    <t>涨跌bp</t>
+  </si>
+  <si>
+    <t>成交笔数</t>
+  </si>
+  <si>
+    <t>GVN笔数</t>
+  </si>
+  <si>
+    <t>TKN笔数</t>
+  </si>
+  <si>
+    <t>中债(行/到)</t>
+  </si>
+  <si>
+    <t>中债偏离(BP)</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>流动性评分</t>
+  </si>
+  <si>
+    <t>中债隐含评级</t>
+  </si>
+  <si>
+    <t>中证净价</t>
+  </si>
+  <si>
+    <t>主承销商</t>
+  </si>
+  <si>
+    <t>成交偏离(BP)</t>
+  </si>
+  <si>
+    <t>发行日</t>
+  </si>
+  <si>
+    <t>主/债</t>
+  </si>
+  <si>
+    <t>26达州01</t>
+  </si>
+  <si>
+    <t>282655.SH</t>
+  </si>
+  <si>
+    <t>4.77Y</t>
+  </si>
+  <si>
+    <t>2.2300</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2.1931</t>
+  </si>
+  <si>
+    <t>3.69</t>
+  </si>
+  <si>
+    <t>02:06:27</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>100.7772</t>
+  </si>
+  <si>
+    <t>光大证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-4.37</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>AA+/--</t>
+  </si>
+  <si>
+    <t>23农行二级资本债03B</t>
+  </si>
+  <si>
+    <t>232380074.IB</t>
+  </si>
+  <si>
+    <t>7.27Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.0000</t>
+  </si>
+  <si>
+    <t>2.0050</t>
+  </si>
+  <si>
+    <t>-0.50</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2.0126/2.1662</t>
+  </si>
+  <si>
+    <t>-1.26</t>
+  </si>
+  <si>
+    <t>01:24:07</t>
+  </si>
+  <si>
+    <t>110.3439</t>
+  </si>
+  <si>
+    <t>中国国际金融股份有限公司</t>
+  </si>
+  <si>
+    <t>2023-10-26</t>
+  </si>
+  <si>
+    <t>AAA/AAA</t>
+  </si>
+  <si>
+    <t>26金源华兴SCP001</t>
+  </si>
+  <si>
+    <t>012681597.IB</t>
+  </si>
+  <si>
+    <t>243D</t>
+  </si>
+  <si>
+    <t>1.9980</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>00:59:22</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>99.9527</t>
+  </si>
+  <si>
+    <t>渤海银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>23农行二级资本债02B</t>
+  </si>
+  <si>
+    <t>232380053.IB</t>
+  </si>
+  <si>
+    <t>7.15Y+5.00Y</t>
+  </si>
+  <si>
+    <t>1.9950</t>
+  </si>
+  <si>
+    <t>2.0025</t>
+  </si>
+  <si>
+    <t>-0.75</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2.0035/2.1629</t>
+  </si>
+  <si>
+    <t>-0.85</t>
+  </si>
+  <si>
+    <t>02:04:22</t>
+  </si>
+  <si>
+    <t>108.9005</t>
+  </si>
+  <si>
+    <t>2023-09-11</t>
+  </si>
+  <si>
+    <t>22金街03</t>
+  </si>
+  <si>
+    <t>149915.SZ</t>
+  </si>
+  <si>
+    <t>292D</t>
+  </si>
+  <si>
+    <t>1.9300</t>
+  </si>
+  <si>
+    <t>1.9328</t>
+  </si>
+  <si>
+    <t>-0.28</t>
+  </si>
+  <si>
+    <t>02:11:44</t>
+  </si>
+  <si>
+    <t>D-</t>
+  </si>
+  <si>
+    <t>100.5216</t>
+  </si>
+  <si>
+    <t>中信建投证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-4.04</t>
+  </si>
+  <si>
+    <t>2022-05-08</t>
+  </si>
+  <si>
+    <t>24鄂联投MTN005</t>
+  </si>
+  <si>
+    <t>102400819.IB</t>
+  </si>
+  <si>
+    <t>2.91Y</t>
+  </si>
+  <si>
+    <t>1.8800</t>
+  </si>
+  <si>
+    <t>1.8887</t>
+  </si>
+  <si>
+    <t>-0.87</t>
+  </si>
+  <si>
+    <t>01:49:14</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>101.9487</t>
+  </si>
+  <si>
+    <t>国信证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-06-18</t>
+  </si>
+  <si>
+    <t>AAA/--</t>
+  </si>
+  <si>
+    <t>25农行永续债01BC</t>
+  </si>
+  <si>
+    <t>242580017.IB</t>
+  </si>
+  <si>
+    <t>3.85Y+N</t>
+  </si>
+  <si>
+    <t>1.7500</t>
+  </si>
+  <si>
+    <t>1.7650</t>
+  </si>
+  <si>
+    <t>-1.50</t>
+  </si>
+  <si>
+    <t>1.7563/2.1860</t>
+  </si>
+  <si>
+    <t>-0.63</t>
+  </si>
+  <si>
+    <t>02:07:42</t>
+  </si>
+  <si>
+    <t>100.8035</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>25农行二级资本债02A(BC)</t>
+  </si>
+  <si>
+    <t>232580024.IB</t>
+  </si>
+  <si>
+    <t>4.00Y+5.00Y</t>
+  </si>
+  <si>
+    <t>1.7450</t>
+  </si>
+  <si>
+    <t>1.75/2.1200</t>
+  </si>
+  <si>
+    <t>01:38:17</t>
+  </si>
+  <si>
+    <t>101.8071</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>25浙商银行小微债01BC</t>
+  </si>
+  <si>
+    <t>212580007.IB</t>
+  </si>
+  <si>
+    <t>1.71Y</t>
+  </si>
+  <si>
+    <t>1.5250</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>1.5233</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>02:11:48</t>
+  </si>
+  <si>
+    <t>100.5779</t>
+  </si>
+  <si>
+    <t>中信证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>26农业银行CD174</t>
+  </si>
+  <si>
+    <t>112603174.IB</t>
+  </si>
+  <si>
+    <t>274D</t>
+  </si>
+  <si>
+    <t>1.4750</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>01:57:50</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>21农业银行永续债01</t>
+  </si>
+  <si>
+    <t>2128038.IB</t>
+  </si>
+  <si>
+    <t>116D+N</t>
+  </si>
+  <si>
+    <t>1.4600</t>
+  </si>
+  <si>
+    <t>1.4650</t>
+  </si>
+  <si>
+    <t>1.465/1.9031</t>
+  </si>
+  <si>
+    <t>01:54:25</t>
+  </si>
+  <si>
+    <t>100.7102</t>
+  </si>
+  <si>
+    <t>华泰证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2021-11-11</t>
+  </si>
+  <si>
+    <t>26中信银行CD064</t>
+  </si>
+  <si>
+    <t>112608064.IB</t>
+  </si>
+  <si>
+    <t>230D</t>
+  </si>
+  <si>
+    <t>1.4500</t>
+  </si>
+  <si>
+    <t>1.4550</t>
+  </si>
+  <si>
+    <t>01:38:36</t>
+  </si>
+  <si>
+    <t>98.5200</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>26农业银行CD087</t>
+  </si>
+  <si>
+    <t>112603087.IB</t>
+  </si>
+  <si>
+    <t>99D</t>
+  </si>
+  <si>
+    <t>1.4350</t>
+  </si>
+  <si>
+    <t>1.4244</t>
+  </si>
+  <si>
+    <t>1.06</t>
+  </si>
+  <si>
+    <t>02:23:11</t>
+  </si>
+  <si>
+    <t>99.2909</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>26农业银行CD081</t>
+  </si>
+  <si>
+    <t>112603081.IB</t>
+  </si>
+  <si>
+    <t>96D</t>
+  </si>
+  <si>
+    <t>1.4400</t>
+  </si>
+  <si>
+    <t>1.4233</t>
+  </si>
+  <si>
+    <t>1.17</t>
+  </si>
+  <si>
+    <t>02:07:59</t>
+  </si>
+  <si>
+    <t>99.2943</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>26农业银行CD076</t>
+  </si>
+  <si>
+    <t>112603076.IB</t>
+  </si>
+  <si>
+    <t>92D</t>
+  </si>
+  <si>
+    <t>1.4212</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>01:44:02</t>
+  </si>
+  <si>
+    <t>99.2870</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>26农业银行CD048</t>
+  </si>
+  <si>
+    <t>112603048.IB</t>
+  </si>
+  <si>
+    <t>63D</t>
+  </si>
+  <si>
+    <t>1.4150</t>
+  </si>
+  <si>
+    <t>1.4050</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>01:01:27</t>
+  </si>
+  <si>
+    <t>99.2676</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>26中信银行CD160</t>
+  </si>
+  <si>
+    <t>112608160.IB</t>
+  </si>
+  <si>
+    <t>57D</t>
+  </si>
+  <si>
+    <t>1.4100</t>
+  </si>
+  <si>
+    <t>01:35:02</t>
+  </si>
+  <si>
+    <t>99.6396</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>26农业银行CD093</t>
+  </si>
+  <si>
+    <t>112603093.IB</t>
+  </si>
+  <si>
+    <t>21D</t>
+  </si>
+  <si>
+    <t>1.3950</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>01:33:54</t>
+  </si>
+  <si>
+    <t>99.6497</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>26农业银行CD096</t>
+  </si>
+  <si>
+    <t>112603096.IB</t>
+  </si>
+  <si>
+    <t>22D</t>
+  </si>
+  <si>
+    <t>01:00:52</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>26中信银行CD166</t>
+  </si>
+  <si>
+    <t>112608166.IB</t>
+  </si>
+  <si>
+    <t>68D</t>
+  </si>
+  <si>
+    <t>1.4000</t>
+  </si>
+  <si>
+    <t>-1.00</t>
+  </si>
+  <si>
+    <t>01:31:30</t>
+  </si>
+  <si>
+    <t>99.6402</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
   </si>
   <si>
     <t>成交日期</t>
   </si>
   <si>
-    <t>债券简称</t>
-  </si>
-  <si>
-    <t>剩余期限</t>
-  </si>
-  <si>
-    <t>最新成交</t>
-  </si>
-  <si>
     <t>中债/中证</t>
   </si>
   <si>
-    <t>中债偏离(BP)</t>
-  </si>
-  <si>
     <t>发行人</t>
   </si>
   <si>
     <t>区域</t>
   </si>
   <si>
-    <t>债券代码</t>
-  </si>
-  <si>
-    <t>中债隐含评级</t>
-  </si>
-  <si>
-    <t>主/债</t>
+    <t>2026-7-23</t>
+  </si>
+  <si>
+    <t>达州市投资有限公司</t>
+  </si>
+  <si>
+    <t>四川</t>
+  </si>
+  <si>
+    <t>中国农业银行股份有限公司</t>
+  </si>
+  <si>
+    <t>北京</t>
+  </si>
+  <si>
+    <t>金源华兴融资租赁有限公司</t>
+  </si>
+  <si>
+    <t>江西</t>
+  </si>
+  <si>
+    <t>金融街控股股份有限公司</t>
+  </si>
+  <si>
+    <t>湖北省联合发展投资集团有限公司</t>
+  </si>
+  <si>
+    <t>湖北</t>
+  </si>
+  <si>
+    <t>浙商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>浙江</t>
+  </si>
+  <si>
+    <t>中信银行股份有限公司</t>
   </si>
   <si>
     <t>2026-7-22</t>
@@ -78,12 +753,6 @@
     <t>102483483.IB</t>
   </si>
   <si>
-    <t>**</t>
-  </si>
-  <si>
-    <t>AAA/--</t>
-  </si>
-  <si>
     <t>25泸租01</t>
   </si>
   <si>
@@ -102,9 +771,6 @@
     <t>泸州发展融资租赁有限公司</t>
   </si>
   <si>
-    <t>四川</t>
-  </si>
-  <si>
     <t>257538.SH</t>
   </si>
   <si>
@@ -135,9 +801,6 @@
     <t>134124.SZ</t>
   </si>
   <si>
-    <t>AA+/--</t>
-  </si>
-  <si>
     <t>25日发01</t>
   </si>
   <si>
@@ -264,9 +927,6 @@
     <t>21彭水债</t>
   </si>
   <si>
-    <t>1.71Y</t>
-  </si>
-  <si>
     <t>1.8500</t>
   </si>
   <si>
@@ -318,18 +978,9 @@
     <t>-0.61</t>
   </si>
   <si>
-    <t>中国农业银行股份有限公司</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
     <t>312610002.IB</t>
   </si>
   <si>
-    <t>AAA/AAA</t>
-  </si>
-  <si>
     <t>25农行二级资本债01A(BC)</t>
   </si>
   <si>
@@ -382,9 +1033,6 @@
   </si>
   <si>
     <t>-0.13</t>
-  </si>
-  <si>
-    <t>中信银行股份有限公司</t>
   </si>
   <si>
     <t>2528006.IB</t>
@@ -764,15 +1412,1514 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="26" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V3" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>60</v>
+      </c>
+      <c r="R4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4" t="s">
+        <v>62</v>
+      </c>
+      <c r="U4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V4" t="s">
+        <v>63</v>
+      </c>
+      <c r="W4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" t="s">
+        <v>74</v>
+      </c>
+      <c r="P5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" t="s">
+        <v>76</v>
+      </c>
+      <c r="T5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" t="s">
+        <v>74</v>
+      </c>
+      <c r="V5" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>85</v>
+      </c>
+      <c r="R6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" t="s">
+        <v>86</v>
+      </c>
+      <c r="T6" t="s">
+        <v>87</v>
+      </c>
+      <c r="U6" t="s">
+        <v>88</v>
+      </c>
+      <c r="V6" t="s">
+        <v>89</v>
+      </c>
+      <c r="W6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O7" t="s">
+        <v>95</v>
+      </c>
+      <c r="P7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>97</v>
+      </c>
+      <c r="R7" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" t="s">
+        <v>98</v>
+      </c>
+      <c r="T7" t="s">
+        <v>99</v>
+      </c>
+      <c r="U7" t="s">
+        <v>95</v>
+      </c>
+      <c r="V7" t="s">
+        <v>100</v>
+      </c>
+      <c r="W7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" t="s">
+        <v>109</v>
+      </c>
+      <c r="P8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" t="s">
+        <v>34</v>
+      </c>
+      <c r="S8" t="s">
+        <v>111</v>
+      </c>
+      <c r="T8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" t="s">
+        <v>109</v>
+      </c>
+      <c r="V8" t="s">
+        <v>112</v>
+      </c>
+      <c r="W8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" t="s">
+        <v>117</v>
+      </c>
+      <c r="O9" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U9" t="s">
+        <v>45</v>
+      </c>
+      <c r="V9" t="s">
+        <v>120</v>
+      </c>
+      <c r="W9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" t="s">
+        <v>126</v>
+      </c>
+      <c r="O10" t="s">
+        <v>127</v>
+      </c>
+      <c r="P10" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
+        <v>129</v>
+      </c>
+      <c r="T10" t="s">
+        <v>130</v>
+      </c>
+      <c r="U10" t="s">
+        <v>127</v>
+      </c>
+      <c r="V10" t="s">
+        <v>131</v>
+      </c>
+      <c r="W10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
+        <v>71</v>
+      </c>
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" t="s">
+        <v>136</v>
+      </c>
+      <c r="P11" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" t="s">
+        <v>136</v>
+      </c>
+      <c r="V11" t="s">
+        <v>138</v>
+      </c>
+      <c r="W11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" t="s">
+        <v>143</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" t="s">
+        <v>144</v>
+      </c>
+      <c r="O12" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>33</v>
+      </c>
+      <c r="R12" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" t="s">
+        <v>146</v>
+      </c>
+      <c r="T12" t="s">
+        <v>147</v>
+      </c>
+      <c r="U12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V12" t="s">
+        <v>148</v>
+      </c>
+      <c r="W12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H13" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" t="s">
+        <v>153</v>
+      </c>
+      <c r="O13" t="s">
+        <v>45</v>
+      </c>
+      <c r="P13" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>27</v>
+      </c>
+      <c r="R13" t="s">
+        <v>34</v>
+      </c>
+      <c r="S13" t="s">
+        <v>155</v>
+      </c>
+      <c r="T13" t="s">
+        <v>27</v>
+      </c>
+      <c r="U13" t="s">
+        <v>45</v>
+      </c>
+      <c r="V13" t="s">
+        <v>156</v>
+      </c>
+      <c r="W13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" t="s">
+        <v>161</v>
+      </c>
+      <c r="O14" t="s">
+        <v>162</v>
+      </c>
+      <c r="P14" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" t="s">
+        <v>34</v>
+      </c>
+      <c r="S14" t="s">
+        <v>164</v>
+      </c>
+      <c r="T14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U14" t="s">
+        <v>162</v>
+      </c>
+      <c r="V14" t="s">
+        <v>165</v>
+      </c>
+      <c r="W14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" t="s">
+        <v>170</v>
+      </c>
+      <c r="O15" t="s">
+        <v>171</v>
+      </c>
+      <c r="P15" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>27</v>
+      </c>
+      <c r="R15" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" t="s">
+        <v>173</v>
+      </c>
+      <c r="T15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U15" t="s">
+        <v>171</v>
+      </c>
+      <c r="V15" t="s">
+        <v>174</v>
+      </c>
+      <c r="W15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F16" t="s">
+        <v>160</v>
+      </c>
+      <c r="G16" t="s">
+        <v>160</v>
+      </c>
+      <c r="H16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" t="s">
+        <v>178</v>
+      </c>
+      <c r="O16" t="s">
+        <v>179</v>
+      </c>
+      <c r="P16" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>27</v>
+      </c>
+      <c r="R16" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" t="s">
+        <v>181</v>
+      </c>
+      <c r="T16" t="s">
+        <v>27</v>
+      </c>
+      <c r="U16" t="s">
+        <v>179</v>
+      </c>
+      <c r="V16" t="s">
+        <v>182</v>
+      </c>
+      <c r="W16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G17" t="s">
+        <v>186</v>
+      </c>
+      <c r="H17" t="s">
+        <v>186</v>
+      </c>
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" t="s">
+        <v>187</v>
+      </c>
+      <c r="O17" t="s">
+        <v>188</v>
+      </c>
+      <c r="P17" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>27</v>
+      </c>
+      <c r="R17" t="s">
+        <v>34</v>
+      </c>
+      <c r="S17" t="s">
+        <v>190</v>
+      </c>
+      <c r="T17" t="s">
+        <v>27</v>
+      </c>
+      <c r="U17" t="s">
+        <v>188</v>
+      </c>
+      <c r="V17" t="s">
+        <v>191</v>
+      </c>
+      <c r="W17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G18" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" t="s">
+        <v>195</v>
+      </c>
+      <c r="O18" t="s">
+        <v>125</v>
+      </c>
+      <c r="P18" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>27</v>
+      </c>
+      <c r="R18" t="s">
+        <v>34</v>
+      </c>
+      <c r="S18" t="s">
+        <v>197</v>
+      </c>
+      <c r="T18" t="s">
+        <v>27</v>
+      </c>
+      <c r="U18" t="s">
+        <v>125</v>
+      </c>
+      <c r="V18" t="s">
+        <v>198</v>
+      </c>
+      <c r="W18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" t="s">
+        <v>195</v>
+      </c>
+      <c r="F19" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" t="s">
+        <v>195</v>
+      </c>
+      <c r="H19" t="s">
+        <v>195</v>
+      </c>
+      <c r="I19" t="s">
+        <v>186</v>
+      </c>
+      <c r="J19" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" t="s">
+        <v>72</v>
+      </c>
+      <c r="L19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" t="s">
+        <v>72</v>
+      </c>
+      <c r="N19" t="s">
+        <v>202</v>
+      </c>
+      <c r="O19" t="s">
+        <v>203</v>
+      </c>
+      <c r="P19" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R19" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" t="s">
+        <v>205</v>
+      </c>
+      <c r="T19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U19" t="s">
+        <v>203</v>
+      </c>
+      <c r="V19" t="s">
+        <v>206</v>
+      </c>
+      <c r="W19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" t="s">
+        <v>195</v>
+      </c>
+      <c r="F20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" t="s">
+        <v>195</v>
+      </c>
+      <c r="I20" t="s">
+        <v>195</v>
+      </c>
+      <c r="J20" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20" t="s">
+        <v>202</v>
+      </c>
+      <c r="O20" t="s">
+        <v>203</v>
+      </c>
+      <c r="P20" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>27</v>
+      </c>
+      <c r="R20" t="s">
+        <v>34</v>
+      </c>
+      <c r="S20" t="s">
+        <v>205</v>
+      </c>
+      <c r="T20" t="s">
+        <v>27</v>
+      </c>
+      <c r="U20" t="s">
+        <v>203</v>
+      </c>
+      <c r="V20" t="s">
+        <v>211</v>
+      </c>
+      <c r="W20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F21" t="s">
+        <v>215</v>
+      </c>
+      <c r="G21" t="s">
+        <v>215</v>
+      </c>
+      <c r="H21" t="s">
+        <v>215</v>
+      </c>
+      <c r="I21" t="s">
+        <v>186</v>
+      </c>
+      <c r="J21" t="s">
+        <v>107</v>
+      </c>
+      <c r="K21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N21" t="s">
+        <v>195</v>
+      </c>
+      <c r="O21" t="s">
+        <v>216</v>
+      </c>
+      <c r="P21" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" t="s">
+        <v>34</v>
+      </c>
+      <c r="S21" t="s">
+        <v>218</v>
+      </c>
+      <c r="T21" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" t="s">
+        <v>216</v>
+      </c>
+      <c r="V21" t="s">
+        <v>219</v>
+      </c>
+      <c r="W21" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -783,50 +2930,754 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K1" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H6" t="s">
+        <v>228</v>
+      </c>
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" t="s">
+        <v>232</v>
+      </c>
+      <c r="H7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" t="s">
+        <v>228</v>
+      </c>
+      <c r="I8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" t="s">
+        <v>228</v>
+      </c>
+      <c r="I11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I12" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s">
+        <v>236</v>
+      </c>
+      <c r="H13" t="s">
+        <v>228</v>
+      </c>
+      <c r="I13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" t="s">
+        <v>228</v>
+      </c>
+      <c r="I14" t="s">
+        <v>158</v>
+      </c>
+      <c r="J14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" t="s">
+        <v>228</v>
+      </c>
+      <c r="I15" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" t="s">
+        <v>227</v>
+      </c>
+      <c r="H16" t="s">
+        <v>228</v>
+      </c>
+      <c r="I16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" t="s">
+        <v>228</v>
+      </c>
+      <c r="I17" t="s">
+        <v>184</v>
+      </c>
+      <c r="J17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F18" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" t="s">
+        <v>236</v>
+      </c>
+      <c r="H18" t="s">
+        <v>228</v>
+      </c>
+      <c r="I18" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G19" t="s">
+        <v>227</v>
+      </c>
+      <c r="H19" t="s">
+        <v>228</v>
+      </c>
+      <c r="I19" t="s">
+        <v>200</v>
+      </c>
+      <c r="J19" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G20" t="s">
+        <v>227</v>
+      </c>
+      <c r="H20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I20" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" t="s">
+        <v>216</v>
+      </c>
+      <c r="G21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H21" t="s">
+        <v>228</v>
+      </c>
+      <c r="I21" t="s">
+        <v>213</v>
+      </c>
+      <c r="J21" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -837,7 +3688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -854,527 +3705,1227 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>242</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>249</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>226</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>252</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>254</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>255</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>256</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>257</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>258</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>259</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>260</v>
       </c>
       <c r="I4" t="s">
+        <v>261</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
         <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>262</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>263</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>265</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>260</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>268</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>271</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>272</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>273</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>274</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>275</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>276</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>279</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>280</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>281</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>282</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>283</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>284</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>285</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>287</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>288</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>289</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>290</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>291</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>292</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>293</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>295</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>297</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>305</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>306</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>307</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>308</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>309</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>310</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>311</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>312</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>313</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>226</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>315</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>316</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>317</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>319</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="G12" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="H12" t="s">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>321</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K12" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>322</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>323</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>324</v>
       </c>
       <c r="E13" t="s">
-        <v>108</v>
+        <v>325</v>
       </c>
       <c r="F13" t="s">
-        <v>109</v>
+        <v>326</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="H13" t="s">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="I13" t="s">
-        <v>110</v>
+        <v>327</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K13" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>328</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>329</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>330</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>331</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>332</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>333</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>284</v>
       </c>
       <c r="I14" t="s">
-        <v>117</v>
+        <v>334</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>335</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>336</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>337</v>
       </c>
       <c r="E15" t="s">
+        <v>338</v>
+      </c>
+      <c r="F15" t="s">
+        <v>339</v>
+      </c>
+      <c r="G15" t="s">
+        <v>236</v>
+      </c>
+      <c r="H15" t="s">
+        <v>228</v>
+      </c>
+      <c r="I15" t="s">
+        <v>340</v>
+      </c>
+      <c r="J15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" t="s">
+        <v>225</v>
+      </c>
+      <c r="H16" t="s">
+        <v>226</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" t="s">
+        <v>228</v>
+      </c>
+      <c r="I17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
+        <v>229</v>
+      </c>
+      <c r="H18" t="s">
+        <v>230</v>
+      </c>
+      <c r="I18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s">
+        <v>227</v>
+      </c>
+      <c r="H19" t="s">
+        <v>228</v>
+      </c>
+      <c r="I19" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" t="s">
+        <v>231</v>
+      </c>
+      <c r="H20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" t="s">
+        <v>232</v>
+      </c>
+      <c r="H21" t="s">
+        <v>233</v>
+      </c>
+      <c r="I21" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" t="s">
+        <v>227</v>
+      </c>
+      <c r="H22" t="s">
+        <v>228</v>
+      </c>
+      <c r="I22" t="s">
+        <v>103</v>
+      </c>
+      <c r="J22" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" t="s">
+        <v>227</v>
+      </c>
+      <c r="H23" t="s">
+        <v>228</v>
+      </c>
+      <c r="I23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>224</v>
+      </c>
+      <c r="B24" t="s">
         <v>121</v>
       </c>
-      <c r="F15" t="s">
+      <c r="C24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" t="s">
+        <v>234</v>
+      </c>
+      <c r="H24" t="s">
+        <v>235</v>
+      </c>
+      <c r="I24" t="s">
         <v>122</v>
       </c>
-      <c r="G15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" t="s">
-        <v>102</v>
-      </c>
-      <c r="I15" t="s">
-        <v>124</v>
-      </c>
-      <c r="J15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>104</v>
+      <c r="J24" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" t="s">
+        <v>227</v>
+      </c>
+      <c r="H25" t="s">
+        <v>228</v>
+      </c>
+      <c r="I25" t="s">
+        <v>133</v>
+      </c>
+      <c r="J25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" t="s">
+        <v>227</v>
+      </c>
+      <c r="H26" t="s">
+        <v>228</v>
+      </c>
+      <c r="I26" t="s">
+        <v>140</v>
+      </c>
+      <c r="J26" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>224</v>
+      </c>
+      <c r="B27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" t="s">
+        <v>236</v>
+      </c>
+      <c r="H27" t="s">
+        <v>228</v>
+      </c>
+      <c r="I27" t="s">
+        <v>150</v>
+      </c>
+      <c r="J27" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" t="s">
+        <v>227</v>
+      </c>
+      <c r="H28" t="s">
+        <v>228</v>
+      </c>
+      <c r="I28" t="s">
+        <v>158</v>
+      </c>
+      <c r="J28" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" t="s">
+        <v>171</v>
+      </c>
+      <c r="G29" t="s">
+        <v>227</v>
+      </c>
+      <c r="H29" t="s">
+        <v>228</v>
+      </c>
+      <c r="I29" t="s">
+        <v>167</v>
+      </c>
+      <c r="J29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30" t="s">
+        <v>179</v>
+      </c>
+      <c r="G30" t="s">
+        <v>227</v>
+      </c>
+      <c r="H30" t="s">
+        <v>228</v>
+      </c>
+      <c r="I30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31" t="s">
+        <v>183</v>
+      </c>
+      <c r="C31" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" t="s">
+        <v>187</v>
+      </c>
+      <c r="F31" t="s">
+        <v>188</v>
+      </c>
+      <c r="G31" t="s">
+        <v>227</v>
+      </c>
+      <c r="H31" t="s">
+        <v>228</v>
+      </c>
+      <c r="I31" t="s">
+        <v>184</v>
+      </c>
+      <c r="J31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>224</v>
+      </c>
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" t="s">
+        <v>195</v>
+      </c>
+      <c r="F32" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" t="s">
+        <v>236</v>
+      </c>
+      <c r="H32" t="s">
+        <v>228</v>
+      </c>
+      <c r="I32" t="s">
+        <v>193</v>
+      </c>
+      <c r="J32" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" t="s">
+        <v>202</v>
+      </c>
+      <c r="F33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G33" t="s">
+        <v>227</v>
+      </c>
+      <c r="H33" t="s">
+        <v>228</v>
+      </c>
+      <c r="I33" t="s">
+        <v>200</v>
+      </c>
+      <c r="J33" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>224</v>
+      </c>
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" t="s">
+        <v>209</v>
+      </c>
+      <c r="D34" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" t="s">
+        <v>203</v>
+      </c>
+      <c r="G34" t="s">
+        <v>227</v>
+      </c>
+      <c r="H34" t="s">
+        <v>228</v>
+      </c>
+      <c r="I34" t="s">
+        <v>208</v>
+      </c>
+      <c r="J34" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35" t="s">
+        <v>216</v>
+      </c>
+      <c r="G35" t="s">
+        <v>236</v>
+      </c>
+      <c r="H35" t="s">
+        <v>228</v>
+      </c>
+      <c r="I35" t="s">
+        <v>213</v>
+      </c>
+      <c r="J35" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/secondary2/secondary_quote_2026-07-23.xlsx
+++ b/data/secondary2/secondary_quote_2026-07-23.xlsx
@@ -387,7 +387,7 @@
     <t>-0.09</t>
   </si>
   <si>
-    <t>07:01:50</t>
+    <t>08:12:39</t>
   </si>
   <si>
     <t>103.2287</t>
@@ -1983,13 +1983,13 @@
         <v>121</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
       <c r="M9" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N9" t="s">
         <v>122</v>
@@ -2267,13 +2267,13 @@
         <v>164</v>
       </c>
       <c r="K13" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L13" t="s">
         <v>71</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="N13" t="s">
         <v>165</v>

--- a/data/secondary2/secondary_quote_2026-07-23.xlsx
+++ b/data/secondary2/secondary_quote_2026-07-23.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="293">
   <si>
     <t>债券简称</t>
   </si>
@@ -183,13 +183,16 @@
     <t>--</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2.1931</t>
   </si>
   <si>
     <t>3.69</t>
   </si>
   <si>
-    <t>02:06:27</t>
+    <t>08:52:09</t>
   </si>
   <si>
     <t>S</t>
@@ -210,6 +213,42 @@
     <t>AA+/--</t>
   </si>
   <si>
+    <t>26成都经开PPN001A</t>
+  </si>
+  <si>
+    <t>032680038.IB</t>
+  </si>
+  <si>
+    <t>4.48Y</t>
+  </si>
+  <si>
+    <t>2.2000</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2.2129</t>
+  </si>
+  <si>
+    <t>-1.29</t>
+  </si>
+  <si>
+    <t>08:47:47</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>102.8437</t>
+  </si>
+  <si>
+    <t>国金证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-01-11</t>
+  </si>
+  <si>
     <t>25农行二级资本债04B(BC)</t>
   </si>
   <si>
@@ -228,9 +267,6 @@
     <t>-0.75</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2.1285/2.2546</t>
   </si>
   <si>
@@ -264,10 +300,19 @@
     <t>9.16Y+5.00Y</t>
   </si>
   <si>
+    <t>2.1275</t>
+  </si>
+  <si>
     <t>2.1250</t>
   </si>
   <si>
-    <t>2.1288</t>
+    <t>2.1285</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>4</t>
@@ -276,10 +321,7 @@
     <t>2.126/2.2495</t>
   </si>
   <si>
-    <t>-0.10</t>
-  </si>
-  <si>
-    <t>06:17:20</t>
+    <t>09:00:10</t>
   </si>
   <si>
     <t>S+</t>
@@ -291,324 +333,348 @@
     <t>2025-09-16</t>
   </si>
   <si>
-    <t>25农行二级资本债01B(BC)</t>
-  </si>
-  <si>
-    <t>232580017.IB</t>
-  </si>
-  <si>
-    <t>8.90Y+5.00Y</t>
+    <t>25农行二级资本债02B(BC)</t>
+  </si>
+  <si>
+    <t>232580025.IB</t>
+  </si>
+  <si>
+    <t>9.00Y+5.00Y</t>
   </si>
   <si>
     <t>2.1150</t>
   </si>
   <si>
-    <t>2.1130</t>
+    <t>2.12/2.2142</t>
+  </si>
+  <si>
+    <t>-0.50</t>
+  </si>
+  <si>
+    <t>08:47:16</t>
+  </si>
+  <si>
+    <t>101.0088</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>25长开G2</t>
+  </si>
+  <si>
+    <t>242490.SH</t>
+  </si>
+  <si>
+    <t>3.60Y</t>
+  </si>
+  <si>
+    <t>2.0600</t>
+  </si>
+  <si>
+    <t>2.0746</t>
+  </si>
+  <si>
+    <t>-1.46</t>
+  </si>
+  <si>
+    <t>03:36:12</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>104.4302</t>
+  </si>
+  <si>
+    <t>东海证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-1.59</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>24涪陵国资MTN004B</t>
+  </si>
+  <si>
+    <t>102400790.IB</t>
+  </si>
+  <si>
+    <t>4.87Y</t>
+  </si>
+  <si>
+    <t>2.0500</t>
+  </si>
+  <si>
+    <t>2.0968</t>
+  </si>
+  <si>
+    <t>-4.68</t>
+  </si>
+  <si>
+    <t>06:30:55</t>
+  </si>
+  <si>
+    <t>103.9594</t>
+  </si>
+  <si>
+    <t>中信证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>24农行二级资本债02B</t>
+  </si>
+  <si>
+    <t>232480012.IB</t>
+  </si>
+  <si>
+    <t>7.76Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.0450</t>
+  </si>
+  <si>
+    <t>2.0400</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>2.0459/2.1792</t>
+  </si>
+  <si>
+    <t>-0.09</t>
+  </si>
+  <si>
+    <t>08:26:16</t>
+  </si>
+  <si>
+    <t>103.2287</t>
+  </si>
+  <si>
+    <t>2024-04-22</t>
+  </si>
+  <si>
+    <t>25农行TLAC非资本债02C(BC)</t>
+  </si>
+  <si>
+    <t>242680006.IB</t>
+  </si>
+  <si>
+    <t>4.80Y+N</t>
+  </si>
+  <si>
+    <t>-1.00</t>
+  </si>
+  <si>
+    <t>2.054/2.4744</t>
+  </si>
+  <si>
+    <t>-1.40</t>
+  </si>
+  <si>
+    <t>05:02:09</t>
+  </si>
+  <si>
+    <t>100.5755</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>312510011.IB</t>
+  </si>
+  <si>
+    <t>9.04Y+1.00Y</t>
+  </si>
+  <si>
+    <t>2.0350</t>
+  </si>
+  <si>
+    <t>2.0300</t>
+  </si>
+  <si>
+    <t>2.0325</t>
+  </si>
+  <si>
+    <t>2.0250</t>
+  </si>
+  <si>
+    <t>2.025/2.0956</t>
+  </si>
+  <si>
+    <t>07:52:23</t>
+  </si>
+  <si>
+    <t>101.0204</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>24农行二级资本债01B</t>
+  </si>
+  <si>
+    <t>232480005.IB</t>
+  </si>
+  <si>
+    <t>7.54Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.0275</t>
+  </si>
+  <si>
+    <t>2.0310</t>
+  </si>
+  <si>
+    <t>2.0200</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2.0312/2.1733</t>
+  </si>
+  <si>
+    <t>-0.37</t>
+  </si>
+  <si>
+    <t>07:30:12</t>
+  </si>
+  <si>
+    <t>105.3234</t>
+  </si>
+  <si>
+    <t>2024-02-01</t>
+  </si>
+  <si>
+    <t>26国耀K1</t>
+  </si>
+  <si>
+    <t>245347.SH</t>
+  </si>
+  <si>
+    <t>2.90Y</t>
+  </si>
+  <si>
+    <t>-2.00</t>
+  </si>
+  <si>
+    <t>2.0442</t>
+  </si>
+  <si>
+    <t>-1.42</t>
+  </si>
+  <si>
+    <t>08:02:48</t>
+  </si>
+  <si>
+    <t>99.5188</t>
+  </si>
+  <si>
+    <t>国泰海通证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-1.99</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>23农行二级资本债03B</t>
+  </si>
+  <si>
+    <t>232380074.IB</t>
+  </si>
+  <si>
+    <t>7.27Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.0100</t>
+  </si>
+  <si>
+    <t>2.0000</t>
+  </si>
+  <si>
+    <t>2.0080</t>
+  </si>
+  <si>
+    <t>2.0050</t>
+  </si>
+  <si>
+    <t>2.0126/2.1662</t>
+  </si>
+  <si>
+    <t>-0.26</t>
+  </si>
+  <si>
+    <t>06:30:32</t>
+  </si>
+  <si>
+    <t>110.3439</t>
+  </si>
+  <si>
+    <t>2023-10-26</t>
+  </si>
+  <si>
+    <t>26金源华兴SCP001</t>
+  </si>
+  <si>
+    <t>012681597.IB</t>
+  </si>
+  <si>
+    <t>243D</t>
+  </si>
+  <si>
+    <t>1.9980</t>
   </si>
   <si>
     <t>0.20</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2.1175/2.2114</t>
+    <t>00:59:22</t>
+  </si>
+  <si>
+    <t>99.9527</t>
+  </si>
+  <si>
+    <t>渤海银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>23农行二级资本债02B</t>
+  </si>
+  <si>
+    <t>232380053.IB</t>
+  </si>
+  <si>
+    <t>7.15Y+5.00Y</t>
+  </si>
+  <si>
+    <t>1.9950</t>
+  </si>
+  <si>
+    <t>2.0025</t>
+  </si>
+  <si>
+    <t>1.9981</t>
   </si>
   <si>
     <t>-0.25</t>
   </si>
   <si>
-    <t>06:55:56</t>
-  </si>
-  <si>
-    <t>100.8958</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>24涪陵国资MTN004B</t>
-  </si>
-  <si>
-    <t>102400790.IB</t>
-  </si>
-  <si>
-    <t>4.87Y</t>
-  </si>
-  <si>
-    <t>2.0500</t>
-  </si>
-  <si>
-    <t>2.0968</t>
-  </si>
-  <si>
-    <t>-4.68</t>
-  </si>
-  <si>
-    <t>06:30:55</t>
-  </si>
-  <si>
-    <t>D+</t>
-  </si>
-  <si>
-    <t>103.9594</t>
-  </si>
-  <si>
-    <t>中信证券股份有限公司</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>24农行二级资本债02B</t>
-  </si>
-  <si>
-    <t>232480012.IB</t>
-  </si>
-  <si>
-    <t>7.76Y+5.00Y</t>
-  </si>
-  <si>
-    <t>2.0450</t>
-  </si>
-  <si>
-    <t>2.0400</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>2.0459/2.1792</t>
-  </si>
-  <si>
-    <t>-0.09</t>
-  </si>
-  <si>
-    <t>08:12:39</t>
-  </si>
-  <si>
-    <t>103.2287</t>
-  </si>
-  <si>
-    <t>2024-04-22</t>
-  </si>
-  <si>
-    <t>26恒丰银行永续债01</t>
-  </si>
-  <si>
-    <t>242680006.IB</t>
-  </si>
-  <si>
-    <t>4.80Y+N</t>
-  </si>
-  <si>
-    <t>-1.00</t>
-  </si>
-  <si>
-    <t>2.054/2.4744</t>
-  </si>
-  <si>
-    <t>-1.40</t>
-  </si>
-  <si>
-    <t>05:02:09</t>
-  </si>
-  <si>
-    <t>100.5755</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>25农行TLAC非资本债02C(BC)</t>
-  </si>
-  <si>
-    <t>312510011.IB</t>
-  </si>
-  <si>
-    <t>9.04Y+1.00Y</t>
-  </si>
-  <si>
-    <t>2.0350</t>
-  </si>
-  <si>
-    <t>2.0300</t>
-  </si>
-  <si>
-    <t>2.0325</t>
-  </si>
-  <si>
-    <t>2.0250</t>
-  </si>
-  <si>
-    <t>2.025/2.0956</t>
-  </si>
-  <si>
-    <t>07:52:23</t>
-  </si>
-  <si>
-    <t>101.0204</t>
-  </si>
-  <si>
-    <t>2025-07-31</t>
-  </si>
-  <si>
-    <t>24农行二级资本债01B</t>
-  </si>
-  <si>
-    <t>232480005.IB</t>
-  </si>
-  <si>
-    <t>7.54Y+5.00Y</t>
-  </si>
-  <si>
-    <t>2.0275</t>
-  </si>
-  <si>
-    <t>2.0310</t>
-  </si>
-  <si>
-    <t>2.0200</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>2.0312/2.1733</t>
-  </si>
-  <si>
-    <t>-0.37</t>
-  </si>
-  <si>
-    <t>07:30:12</t>
-  </si>
-  <si>
-    <t>105.3234</t>
-  </si>
-  <si>
-    <t>2024-02-01</t>
-  </si>
-  <si>
-    <t>26国耀K1</t>
-  </si>
-  <si>
-    <t>245347.SH</t>
-  </si>
-  <si>
-    <t>2.90Y</t>
-  </si>
-  <si>
-    <t>-2.00</t>
-  </si>
-  <si>
-    <t>2.0442</t>
-  </si>
-  <si>
-    <t>-1.42</t>
-  </si>
-  <si>
-    <t>08:02:48</t>
-  </si>
-  <si>
-    <t>99.5188</t>
-  </si>
-  <si>
-    <t>国泰海通证券股份有限公司</t>
-  </si>
-  <si>
-    <t>-1.99</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>23农行二级资本债03B</t>
-  </si>
-  <si>
-    <t>232380074.IB</t>
-  </si>
-  <si>
-    <t>7.27Y+5.00Y</t>
-  </si>
-  <si>
-    <t>2.0100</t>
-  </si>
-  <si>
-    <t>2.0000</t>
-  </si>
-  <si>
-    <t>2.0080</t>
-  </si>
-  <si>
-    <t>2.0050</t>
-  </si>
-  <si>
-    <t>2.0126/2.1662</t>
-  </si>
-  <si>
-    <t>-0.26</t>
-  </si>
-  <si>
-    <t>06:30:32</t>
-  </si>
-  <si>
-    <t>110.3439</t>
-  </si>
-  <si>
-    <t>2023-10-26</t>
-  </si>
-  <si>
-    <t>26金源华兴SCP001</t>
-  </si>
-  <si>
-    <t>012681597.IB</t>
-  </si>
-  <si>
-    <t>243D</t>
-  </si>
-  <si>
-    <t>1.9980</t>
-  </si>
-  <si>
-    <t>00:59:22</t>
-  </si>
-  <si>
-    <t>99.9527</t>
-  </si>
-  <si>
-    <t>渤海银行股份有限公司</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>23农行二级资本债02B</t>
-  </si>
-  <si>
-    <t>232380053.IB</t>
-  </si>
-  <si>
-    <t>7.15Y+5.00Y</t>
-  </si>
-  <si>
-    <t>1.9950</t>
-  </si>
-  <si>
-    <t>2.0025</t>
-  </si>
-  <si>
-    <t>1.9981</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
@@ -660,18 +726,24 @@
     <t>四川</t>
   </si>
   <si>
+    <t>成都经开产业投资集团有限公司市政</t>
+  </si>
+  <si>
     <t>中国农业银行股份有限公司</t>
   </si>
   <si>
     <t>北京</t>
   </si>
   <si>
+    <t>重庆长寿开发投资(集团)有限公司</t>
+  </si>
+  <si>
+    <t>重庆</t>
+  </si>
+  <si>
     <t>重庆市涪陵国有资产投资经营集团有限公司</t>
   </si>
   <si>
-    <t>重庆</t>
-  </si>
-  <si>
     <t>恒丰银行股份有限公司</t>
   </si>
   <si>
@@ -820,174 +892,6 @@
   </si>
   <si>
     <t>259335.SH</t>
-  </si>
-  <si>
-    <t>21安工01</t>
-  </si>
-  <si>
-    <t>109D</t>
-  </si>
-  <si>
-    <t>1.9500</t>
-  </si>
-  <si>
-    <t>1.9686</t>
-  </si>
-  <si>
-    <t>-1.86</t>
-  </si>
-  <si>
-    <t>安顺市工业投资股份有限公司</t>
-  </si>
-  <si>
-    <t>贵州</t>
-  </si>
-  <si>
-    <t>197523.SH</t>
-  </si>
-  <si>
-    <t>AA/AAA</t>
-  </si>
-  <si>
-    <t>25津金03</t>
-  </si>
-  <si>
-    <t>1.85Y</t>
-  </si>
-  <si>
-    <t>1.9000</t>
-  </si>
-  <si>
-    <t>1.9121</t>
-  </si>
-  <si>
-    <t>-1.21</t>
-  </si>
-  <si>
-    <t>天津新金融投资有限责任公司</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>134275.SZ</t>
-  </si>
-  <si>
-    <t>21彭水债</t>
-  </si>
-  <si>
-    <t>1.71Y</t>
-  </si>
-  <si>
-    <t>1.8500</t>
-  </si>
-  <si>
-    <t>1.9055</t>
-  </si>
-  <si>
-    <t>-5.55</t>
-  </si>
-  <si>
-    <t>彭水县城市建设投资有限责任公司</t>
-  </si>
-  <si>
-    <t>152808.SH</t>
-  </si>
-  <si>
-    <t>22邛旅01</t>
-  </si>
-  <si>
-    <t>1.08Y</t>
-  </si>
-  <si>
-    <t>1.9946</t>
-  </si>
-  <si>
-    <t>-14.46</t>
-  </si>
-  <si>
-    <t>邛崃市天际山水文化旅游投资集团有限公司</t>
-  </si>
-  <si>
-    <t>184384.SH</t>
-  </si>
-  <si>
-    <t>26农行TLAC非资本债01B(BC)</t>
-  </si>
-  <si>
-    <t>4.73Y+1.00Y</t>
-  </si>
-  <si>
-    <t>1.8300</t>
-  </si>
-  <si>
-    <t>1.8361/1.8815</t>
-  </si>
-  <si>
-    <t>-0.61</t>
-  </si>
-  <si>
-    <t>312610002.IB</t>
-  </si>
-  <si>
-    <t>25农行二级资本债01A(BC)</t>
-  </si>
-  <si>
-    <t>3.90Y+5.00Y</t>
-  </si>
-  <si>
-    <t>1.7350</t>
-  </si>
-  <si>
-    <t>1.7457/2.1400</t>
-  </si>
-  <si>
-    <t>-1.07</t>
-  </si>
-  <si>
-    <t>232580016.IB</t>
-  </si>
-  <si>
-    <t>25衡阳城投PPN005</t>
-  </si>
-  <si>
-    <t>1.93Y+2.00Y</t>
-  </si>
-  <si>
-    <t>1.7300</t>
-  </si>
-  <si>
-    <t>1.7436/1.9582</t>
-  </si>
-  <si>
-    <t>-1.36</t>
-  </si>
-  <si>
-    <t>衡阳市城市建设投资有限公司</t>
-  </si>
-  <si>
-    <t>032580428.IB</t>
-  </si>
-  <si>
-    <t>25中信银行小微债</t>
-  </si>
-  <si>
-    <t>1.68Y</t>
-  </si>
-  <si>
-    <t>1.5000</t>
-  </si>
-  <si>
-    <t>1.5013</t>
-  </si>
-  <si>
-    <t>-0.13</t>
-  </si>
-  <si>
-    <t>中信银行股份有限公司</t>
-  </si>
-  <si>
-    <t>2528006.IB</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -1628,185 +1532,185 @@
         <v>55</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
         <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R4" t="s">
         <v>35</v>
       </c>
       <c r="S4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" t="s">
+        <v>76</v>
+      </c>
+      <c r="U5" t="s">
+        <v>72</v>
+      </c>
+      <c r="V5" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" t="s">
         <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K5" t="s">
-        <v>71</v>
-      </c>
-      <c r="L5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" t="s">
-        <v>73</v>
-      </c>
-      <c r="P5" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R5" t="s">
-        <v>35</v>
-      </c>
-      <c r="S5" t="s">
-        <v>76</v>
-      </c>
-      <c r="T5" t="s">
-        <v>77</v>
-      </c>
-      <c r="U5" t="s">
-        <v>73</v>
-      </c>
-      <c r="V5" t="s">
-        <v>78</v>
-      </c>
-      <c r="W5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
         <v>80</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>81</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" t="s">
         <v>82</v>
       </c>
-      <c r="D6" t="s">
+      <c r="J6" t="s">
         <v>83</v>
       </c>
-      <c r="E6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
         <v>84</v>
       </c>
-      <c r="I6" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="O6" t="s">
         <v>85</v>
       </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="P6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" t="s">
+        <v>88</v>
+      </c>
+      <c r="T6" t="s">
+        <v>89</v>
+      </c>
+      <c r="U6" t="s">
         <v>85</v>
       </c>
-      <c r="N6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O6" t="s">
-        <v>87</v>
-      </c>
-      <c r="P6" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>89</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="V6" t="s">
         <v>90</v>
       </c>
-      <c r="T6" t="s">
-        <v>77</v>
-      </c>
-      <c r="U6" t="s">
-        <v>87</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>91</v>
-      </c>
-      <c r="W6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -1823,114 +1727,114 @@
         <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I7" t="s">
         <v>96</v>
       </c>
       <c r="J7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="M7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P7" t="s">
         <v>102</v>
       </c>
       <c r="Q7" t="s">
+        <v>103</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T7" t="s">
         <v>89</v>
       </c>
-      <c r="R7" t="s">
-        <v>35</v>
-      </c>
-      <c r="S7" t="s">
-        <v>103</v>
-      </c>
-      <c r="T7" t="s">
-        <v>77</v>
-      </c>
       <c r="U7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="V7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" t="s">
         <v>30</v>
       </c>
-      <c r="M8" t="s">
-        <v>71</v>
-      </c>
       <c r="N8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q8" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="R8" t="s">
         <v>35</v>
@@ -1939,87 +1843,87 @@
         <v>113</v>
       </c>
       <c r="T8" t="s">
+        <v>89</v>
+      </c>
+      <c r="U8" t="s">
+        <v>111</v>
+      </c>
+      <c r="V8" t="s">
         <v>114</v>
       </c>
-      <c r="U8" t="s">
-        <v>110</v>
-      </c>
-      <c r="V8" t="s">
-        <v>115</v>
-      </c>
       <c r="W8" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
         <v>116</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>117</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>118</v>
       </c>
-      <c r="D9" t="s">
-        <v>119</v>
-      </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I9" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="J9" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
       <c r="M9" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="N9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O9" t="s">
+        <v>120</v>
+      </c>
+      <c r="P9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q9" t="s">
         <v>122</v>
       </c>
-      <c r="O9" t="s">
+      <c r="R9" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" t="s">
         <v>123</v>
       </c>
-      <c r="P9" t="s">
+      <c r="T9" t="s">
         <v>124</v>
       </c>
-      <c r="Q9" t="s">
-        <v>59</v>
-      </c>
-      <c r="R9" t="s">
-        <v>35</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="U9" t="s">
         <v>125</v>
-      </c>
-      <c r="T9" t="s">
-        <v>114</v>
-      </c>
-      <c r="U9" t="s">
-        <v>123</v>
       </c>
       <c r="V9" t="s">
         <v>126</v>
       </c>
       <c r="W9" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
@@ -2033,34 +1937,34 @@
         <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I10" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="J10" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L10" t="s">
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N10" t="s">
         <v>131</v>
@@ -2072,7 +1976,7 @@
         <v>133</v>
       </c>
       <c r="Q10" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="R10" t="s">
         <v>35</v>
@@ -2081,101 +1985,101 @@
         <v>134</v>
       </c>
       <c r="T10" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="U10" t="s">
         <v>132</v>
       </c>
       <c r="V10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="W10" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
         <v>140</v>
       </c>
       <c r="F11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G11" t="s">
         <v>140</v>
       </c>
       <c r="H11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" t="s">
         <v>141</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>142</v>
       </c>
-      <c r="J11" t="s">
-        <v>28</v>
-      </c>
       <c r="K11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="N11" t="s">
         <v>143</v>
       </c>
       <c r="O11" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="P11" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>60</v>
+      </c>
+      <c r="R11" t="s">
+        <v>35</v>
+      </c>
+      <c r="S11" t="s">
+        <v>146</v>
+      </c>
+      <c r="T11" t="s">
+        <v>135</v>
+      </c>
+      <c r="U11" t="s">
         <v>144</v>
       </c>
-      <c r="Q11" t="s">
-        <v>59</v>
-      </c>
-      <c r="R11" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" t="s">
-        <v>145</v>
-      </c>
-      <c r="T11" t="s">
-        <v>77</v>
-      </c>
-      <c r="U11" t="s">
-        <v>28</v>
-      </c>
       <c r="V11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="W11" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
         <v>141</v>
@@ -2184,268 +2088,268 @@
         <v>141</v>
       </c>
       <c r="G12" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H12" t="s">
+        <v>141</v>
+      </c>
+      <c r="I12" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" t="s">
         <v>151</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" t="s">
+        <v>70</v>
+      </c>
+      <c r="N12" t="s">
         <v>152</v>
       </c>
-      <c r="J12" t="s">
+      <c r="O12" t="s">
         <v>153</v>
       </c>
-      <c r="K12" t="s">
+      <c r="P12" t="s">
         <v>154</v>
       </c>
-      <c r="L12" t="s">
-        <v>29</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="Q12" t="s">
+        <v>60</v>
+      </c>
+      <c r="R12" t="s">
+        <v>35</v>
+      </c>
+      <c r="S12" t="s">
         <v>155</v>
       </c>
-      <c r="N12" t="s">
+      <c r="T12" t="s">
+        <v>89</v>
+      </c>
+      <c r="U12" t="s">
+        <v>153</v>
+      </c>
+      <c r="V12" t="s">
         <v>156</v>
       </c>
-      <c r="O12" t="s">
-        <v>157</v>
-      </c>
-      <c r="P12" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>59</v>
-      </c>
-      <c r="R12" t="s">
-        <v>35</v>
-      </c>
-      <c r="S12" t="s">
-        <v>159</v>
-      </c>
-      <c r="T12" t="s">
-        <v>77</v>
-      </c>
-      <c r="U12" t="s">
-        <v>157</v>
-      </c>
-      <c r="V12" t="s">
-        <v>160</v>
-      </c>
       <c r="W12" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H13" t="s">
         <v>161</v>
       </c>
-      <c r="B13" t="s">
+      <c r="I13" t="s">
         <v>162</v>
       </c>
-      <c r="C13" t="s">
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" t="s">
         <v>163</v>
       </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" t="s">
-        <v>140</v>
-      </c>
-      <c r="F13" t="s">
-        <v>140</v>
-      </c>
-      <c r="G13" t="s">
-        <v>140</v>
-      </c>
-      <c r="H13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I13" t="s">
-        <v>108</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="O13" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" t="s">
         <v>164</v>
       </c>
-      <c r="K13" t="s">
-        <v>98</v>
-      </c>
-      <c r="L13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M13" t="s">
-        <v>85</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="Q13" t="s">
+        <v>60</v>
+      </c>
+      <c r="R13" t="s">
+        <v>35</v>
+      </c>
+      <c r="S13" t="s">
         <v>165</v>
       </c>
-      <c r="O13" t="s">
+      <c r="T13" t="s">
+        <v>89</v>
+      </c>
+      <c r="U13" t="s">
+        <v>28</v>
+      </c>
+      <c r="V13" t="s">
         <v>166</v>
       </c>
-      <c r="P13" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>59</v>
-      </c>
-      <c r="R13" t="s">
-        <v>35</v>
-      </c>
-      <c r="S13" t="s">
-        <v>168</v>
-      </c>
-      <c r="T13" t="s">
-        <v>169</v>
-      </c>
-      <c r="U13" t="s">
-        <v>170</v>
-      </c>
-      <c r="V13" t="s">
-        <v>171</v>
-      </c>
       <c r="W13" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H14" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" t="s">
         <v>172</v>
       </c>
-      <c r="B14" t="s">
+      <c r="J14" t="s">
         <v>173</v>
       </c>
-      <c r="C14" t="s">
+      <c r="K14" t="s">
         <v>174</v>
       </c>
-      <c r="D14" t="s">
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
         <v>175</v>
       </c>
-      <c r="E14" t="s">
+      <c r="N14" t="s">
         <v>176</v>
       </c>
-      <c r="F14" t="s">
-        <v>175</v>
-      </c>
-      <c r="G14" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="O14" t="s">
         <v>177</v>
       </c>
-      <c r="I14" t="s">
+      <c r="P14" t="s">
         <v>178</v>
       </c>
-      <c r="J14" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" t="s">
-        <v>98</v>
-      </c>
-      <c r="L14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" t="s">
-        <v>98</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="Q14" t="s">
+        <v>60</v>
+      </c>
+      <c r="R14" t="s">
+        <v>35</v>
+      </c>
+      <c r="S14" t="s">
         <v>179</v>
       </c>
-      <c r="O14" t="s">
+      <c r="T14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U14" t="s">
+        <v>177</v>
+      </c>
+      <c r="V14" t="s">
         <v>180</v>
       </c>
-      <c r="P14" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>59</v>
-      </c>
-      <c r="R14" t="s">
-        <v>35</v>
-      </c>
-      <c r="S14" t="s">
-        <v>182</v>
-      </c>
-      <c r="T14" t="s">
-        <v>77</v>
-      </c>
-      <c r="U14" t="s">
-        <v>180</v>
-      </c>
-      <c r="V14" t="s">
-        <v>183</v>
-      </c>
       <c r="W14" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" t="s">
         <v>184</v>
       </c>
-      <c r="B15" t="s">
+      <c r="K15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" t="s">
+        <v>70</v>
+      </c>
+      <c r="M15" t="s">
+        <v>100</v>
+      </c>
+      <c r="N15" t="s">
         <v>185</v>
       </c>
-      <c r="C15" t="s">
+      <c r="O15" t="s">
         <v>186</v>
       </c>
-      <c r="D15" t="s">
-        <v>176</v>
-      </c>
-      <c r="E15" t="s">
-        <v>176</v>
-      </c>
-      <c r="F15" t="s">
-        <v>176</v>
-      </c>
-      <c r="G15" t="s">
-        <v>176</v>
-      </c>
-      <c r="H15" t="s">
-        <v>176</v>
-      </c>
-      <c r="I15" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" t="s">
-        <v>71</v>
-      </c>
-      <c r="M15" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="P15" t="s">
         <v>187</v>
       </c>
-      <c r="O15" t="s">
-        <v>97</v>
-      </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
+        <v>60</v>
+      </c>
+      <c r="R15" t="s">
+        <v>35</v>
+      </c>
+      <c r="S15" t="s">
         <v>188</v>
       </c>
-      <c r="Q15" t="s">
-        <v>75</v>
-      </c>
-      <c r="R15" t="s">
-        <v>35</v>
-      </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>189</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
         <v>190</v>
-      </c>
-      <c r="U15" t="s">
-        <v>97</v>
       </c>
       <c r="V15" t="s">
         <v>191</v>
       </c>
       <c r="W15" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
@@ -2459,64 +2363,206 @@
         <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
+        <v>196</v>
+      </c>
+      <c r="F16" t="s">
         <v>195</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>196</v>
-      </c>
-      <c r="G16" t="s">
-        <v>195</v>
       </c>
       <c r="H16" t="s">
         <v>197</v>
       </c>
       <c r="I16" t="s">
+        <v>198</v>
+      </c>
+      <c r="J16" t="s">
+        <v>142</v>
+      </c>
+      <c r="K16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" t="s">
+        <v>199</v>
+      </c>
+      <c r="O16" t="s">
+        <v>200</v>
+      </c>
+      <c r="P16" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>60</v>
+      </c>
+      <c r="R16" t="s">
+        <v>35</v>
+      </c>
+      <c r="S16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T16" t="s">
+        <v>89</v>
+      </c>
+      <c r="U16" t="s">
+        <v>200</v>
+      </c>
+      <c r="V16" t="s">
+        <v>203</v>
+      </c>
+      <c r="W16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" t="s">
         <v>196</v>
       </c>
-      <c r="J16" t="s">
-        <v>101</v>
-      </c>
-      <c r="K16" t="s">
-        <v>198</v>
-      </c>
-      <c r="L16" t="s">
-        <v>199</v>
-      </c>
-      <c r="M16" t="s">
-        <v>200</v>
-      </c>
-      <c r="N16" t="s">
-        <v>201</v>
-      </c>
-      <c r="O16" t="s">
-        <v>202</v>
-      </c>
-      <c r="P16" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>59</v>
-      </c>
-      <c r="R16" t="s">
-        <v>35</v>
-      </c>
-      <c r="S16" t="s">
-        <v>204</v>
-      </c>
-      <c r="T16" t="s">
-        <v>77</v>
-      </c>
-      <c r="U16" t="s">
-        <v>202</v>
-      </c>
-      <c r="V16" t="s">
-        <v>205</v>
-      </c>
-      <c r="W16" t="s">
-        <v>79</v>
+      <c r="E17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F17" t="s">
+        <v>196</v>
+      </c>
+      <c r="G17" t="s">
+        <v>196</v>
+      </c>
+      <c r="H17" t="s">
+        <v>196</v>
+      </c>
+      <c r="I17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" t="s">
+        <v>207</v>
+      </c>
+      <c r="O17" t="s">
+        <v>208</v>
+      </c>
+      <c r="P17" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>87</v>
+      </c>
+      <c r="R17" t="s">
+        <v>35</v>
+      </c>
+      <c r="S17" t="s">
+        <v>210</v>
+      </c>
+      <c r="T17" t="s">
+        <v>211</v>
+      </c>
+      <c r="U17" t="s">
+        <v>208</v>
+      </c>
+      <c r="V17" t="s">
+        <v>212</v>
+      </c>
+      <c r="W17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G18" t="s">
+        <v>216</v>
+      </c>
+      <c r="H18" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" t="s">
+        <v>217</v>
+      </c>
+      <c r="J18" t="s">
+        <v>219</v>
+      </c>
+      <c r="K18" t="s">
+        <v>220</v>
+      </c>
+      <c r="L18" t="s">
+        <v>221</v>
+      </c>
+      <c r="M18" t="s">
+        <v>222</v>
+      </c>
+      <c r="N18" t="s">
+        <v>223</v>
+      </c>
+      <c r="O18" t="s">
+        <v>224</v>
+      </c>
+      <c r="P18" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>60</v>
+      </c>
+      <c r="R18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S18" t="s">
+        <v>226</v>
+      </c>
+      <c r="T18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U18" t="s">
+        <v>224</v>
+      </c>
+      <c r="V18" t="s">
+        <v>227</v>
+      </c>
+      <c r="W18" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2527,7 +2573,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2544,7 +2590,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2556,16 +2602,16 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="F1" t="s">
         <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="H1" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="I1" t="s">
         <v>1</v>
@@ -2579,7 +2625,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -2597,10 +2643,10 @@
         <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="H2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="I2" t="s">
         <v>24</v>
@@ -2614,7 +2660,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -2632,10 +2678,10 @@
         <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="H3" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="I3" t="s">
         <v>41</v>
@@ -2649,7 +2695,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -2661,16 +2707,16 @@
         <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="H4" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="I4" t="s">
         <v>52</v>
@@ -2679,82 +2725,82 @@
         <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
         <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
         <v>80</v>
       </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H6" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J6" t="s">
         <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
         <v>92</v>
@@ -2766,16 +2812,16 @@
         <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H7" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I7" t="s">
         <v>93</v>
@@ -2784,82 +2830,82 @@
         <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" t="s">
+        <v>239</v>
+      </c>
+      <c r="I8" t="s">
         <v>107</v>
       </c>
-      <c r="D8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" t="s">
-        <v>217</v>
-      </c>
-      <c r="H8" t="s">
-        <v>218</v>
-      </c>
-      <c r="I8" t="s">
-        <v>106</v>
-      </c>
       <c r="J8" t="s">
         <v>35</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H9" t="s">
+        <v>241</v>
+      </c>
+      <c r="I9" t="s">
         <v>116</v>
       </c>
-      <c r="C9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" t="s">
-        <v>215</v>
-      </c>
-      <c r="H9" t="s">
-        <v>216</v>
-      </c>
-      <c r="I9" t="s">
-        <v>117</v>
-      </c>
       <c r="J9" t="s">
         <v>35</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B10" t="s">
         <v>127</v>
@@ -2868,7 +2914,7 @@
         <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
         <v>131</v>
@@ -2877,10 +2923,10 @@
         <v>132</v>
       </c>
       <c r="G10" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="H10" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="I10" t="s">
         <v>128</v>
@@ -2889,187 +2935,187 @@
         <v>35</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
         <v>143</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="G11" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H11" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J11" t="s">
         <v>35</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G12" t="s">
+        <v>243</v>
+      </c>
+      <c r="H12" t="s">
+        <v>244</v>
+      </c>
+      <c r="I12" t="s">
         <v>149</v>
       </c>
-      <c r="D12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" t="s">
-        <v>157</v>
-      </c>
-      <c r="G12" t="s">
-        <v>215</v>
-      </c>
-      <c r="H12" t="s">
-        <v>216</v>
-      </c>
-      <c r="I12" t="s">
-        <v>148</v>
-      </c>
       <c r="J12" t="s">
         <v>35</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" t="s">
         <v>163</v>
       </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" t="s">
-        <v>165</v>
-      </c>
       <c r="F13" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="H13" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="I13" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J13" t="s">
         <v>35</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F14" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G14" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H14" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J14" t="s">
         <v>35</v>
       </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" t="s">
         <v>186</v>
       </c>
-      <c r="D15" t="s">
-        <v>176</v>
-      </c>
-      <c r="E15" t="s">
-        <v>187</v>
-      </c>
-      <c r="F15" t="s">
-        <v>97</v>
-      </c>
       <c r="G15" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="H15" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="I15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J15" t="s">
         <v>35</v>
       </c>
       <c r="K15" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B16" t="s">
         <v>192</v>
@@ -3078,19 +3124,19 @@
         <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G16" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H16" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I16" t="s">
         <v>193</v>
@@ -3099,7 +3145,77 @@
         <v>35</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E17" t="s">
+        <v>207</v>
+      </c>
+      <c r="F17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" t="s">
+        <v>247</v>
+      </c>
+      <c r="H17" t="s">
+        <v>248</v>
+      </c>
+      <c r="I17" t="s">
+        <v>205</v>
+      </c>
+      <c r="J17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" t="s">
+        <v>224</v>
+      </c>
+      <c r="G18" t="s">
+        <v>238</v>
+      </c>
+      <c r="H18" t="s">
+        <v>239</v>
+      </c>
+      <c r="I18" t="s">
+        <v>214</v>
+      </c>
+      <c r="J18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3110,7 +3226,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3127,7 +3243,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -3139,16 +3255,16 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="F1" t="s">
         <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="H1" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="I1" t="s">
         <v>1</v>
@@ -3162,31 +3278,31 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="F2" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="H2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="I2" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="J2" t="s">
         <v>35</v>
@@ -3197,982 +3313,772 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="D3" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="E3" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="F3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H3" t="s">
         <v>236</v>
       </c>
-      <c r="G3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H3" t="s">
-        <v>214</v>
-      </c>
       <c r="I3" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="J3" t="s">
         <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="F4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H4" t="s">
         <v>244</v>
       </c>
-      <c r="G4" t="s">
-        <v>245</v>
-      </c>
-      <c r="H4" t="s">
-        <v>220</v>
-      </c>
       <c r="I4" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="J4" t="s">
         <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="C5" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="D5" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="E5" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="F5" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="G5" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="H5" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="I5" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="J5" t="s">
         <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="F6" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="G6" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="H6" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="I6" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="J6" t="s">
         <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C7" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="F7" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G7" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="H7" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="I7" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="J7" t="s">
         <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B8" t="s">
-        <v>269</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>270</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>272</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>273</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="H8" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="I8" t="s">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
         <v>35</v>
       </c>
       <c r="K8" t="s">
-        <v>277</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>280</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>281</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>283</v>
+        <v>233</v>
       </c>
       <c r="H9" t="s">
-        <v>284</v>
+        <v>234</v>
       </c>
       <c r="I9" t="s">
-        <v>285</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
         <v>35</v>
       </c>
       <c r="K9" t="s">
-        <v>277</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B10" t="s">
-        <v>286</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>287</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>288</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>290</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>291</v>
+        <v>235</v>
       </c>
       <c r="H10" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I10" t="s">
-        <v>292</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
         <v>35</v>
       </c>
       <c r="K10" t="s">
-        <v>277</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B11" t="s">
-        <v>293</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="F11" t="s">
-        <v>296</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="H11" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="I11" t="s">
-        <v>298</v>
+        <v>67</v>
       </c>
       <c r="J11" t="s">
         <v>35</v>
       </c>
       <c r="K11" t="s">
-        <v>277</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B12" t="s">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H12" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I12" t="s">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s">
         <v>35</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>305</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>306</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>307</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>308</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H13" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I13" t="s">
-        <v>310</v>
+        <v>93</v>
       </c>
       <c r="J13" t="s">
         <v>35</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B14" t="s">
-        <v>311</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>313</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>315</v>
+        <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>316</v>
+        <v>238</v>
       </c>
       <c r="H14" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="I14" t="s">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="J14" t="s">
         <v>35</v>
       </c>
       <c r="K14" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B15" t="s">
-        <v>318</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>319</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>320</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>321</v>
+        <v>119</v>
       </c>
       <c r="F15" t="s">
-        <v>322</v>
+        <v>120</v>
       </c>
       <c r="G15" t="s">
-        <v>323</v>
+        <v>240</v>
       </c>
       <c r="H15" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="I15" t="s">
-        <v>324</v>
+        <v>116</v>
       </c>
       <c r="J15" t="s">
         <v>35</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="G16" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="H16" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="J16" t="s">
         <v>35</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="G17" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="H17" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="I17" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="J17" t="s">
         <v>35</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="G18" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="H18" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="J18" t="s">
         <v>35</v>
       </c>
       <c r="K18" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H19" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="J19" t="s">
         <v>35</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="G20" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H20" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="I20" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="J20" t="s">
         <v>35</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>186</v>
       </c>
       <c r="G21" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="H21" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="J21" t="s">
         <v>35</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="G22" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="H22" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="J22" t="s">
         <v>35</v>
       </c>
       <c r="K22" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="G23" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="H23" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="I23" t="s">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="J23" t="s">
         <v>35</v>
       </c>
       <c r="K23" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="F24" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="G24" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="H24" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="I24" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="J24" t="s">
         <v>35</v>
       </c>
       <c r="K24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>210</v>
-      </c>
-      <c r="B25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" t="s">
-        <v>138</v>
-      </c>
-      <c r="D25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" t="s">
-        <v>215</v>
-      </c>
-      <c r="H25" t="s">
-        <v>216</v>
-      </c>
-      <c r="I25" t="s">
-        <v>137</v>
-      </c>
-      <c r="J25" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>210</v>
-      </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D26" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" t="s">
-        <v>156</v>
-      </c>
-      <c r="F26" t="s">
-        <v>157</v>
-      </c>
-      <c r="G26" t="s">
-        <v>215</v>
-      </c>
-      <c r="H26" t="s">
-        <v>216</v>
-      </c>
-      <c r="I26" t="s">
-        <v>148</v>
-      </c>
-      <c r="J26" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>210</v>
-      </c>
-      <c r="B27" t="s">
-        <v>161</v>
-      </c>
-      <c r="C27" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" t="s">
-        <v>165</v>
-      </c>
-      <c r="F27" t="s">
-        <v>166</v>
-      </c>
-      <c r="G27" t="s">
-        <v>221</v>
-      </c>
-      <c r="H27" t="s">
-        <v>222</v>
-      </c>
-      <c r="I27" t="s">
-        <v>162</v>
-      </c>
-      <c r="J27" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>210</v>
-      </c>
-      <c r="B28" t="s">
-        <v>172</v>
-      </c>
-      <c r="C28" t="s">
-        <v>174</v>
-      </c>
-      <c r="D28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E28" t="s">
-        <v>179</v>
-      </c>
-      <c r="F28" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" t="s">
-        <v>215</v>
-      </c>
-      <c r="H28" t="s">
-        <v>216</v>
-      </c>
-      <c r="I28" t="s">
-        <v>173</v>
-      </c>
-      <c r="J28" t="s">
-        <v>35</v>
-      </c>
-      <c r="K28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>210</v>
-      </c>
-      <c r="B29" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" t="s">
-        <v>186</v>
-      </c>
-      <c r="D29" t="s">
-        <v>176</v>
-      </c>
-      <c r="E29" t="s">
-        <v>187</v>
-      </c>
-      <c r="F29" t="s">
-        <v>97</v>
-      </c>
-      <c r="G29" t="s">
-        <v>223</v>
-      </c>
-      <c r="H29" t="s">
-        <v>224</v>
-      </c>
-      <c r="I29" t="s">
-        <v>185</v>
-      </c>
-      <c r="J29" t="s">
-        <v>35</v>
-      </c>
-      <c r="K29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>210</v>
-      </c>
-      <c r="B30" t="s">
-        <v>192</v>
-      </c>
-      <c r="C30" t="s">
-        <v>194</v>
-      </c>
-      <c r="D30" t="s">
-        <v>176</v>
-      </c>
-      <c r="E30" t="s">
-        <v>201</v>
-      </c>
-      <c r="F30" t="s">
-        <v>202</v>
-      </c>
-      <c r="G30" t="s">
-        <v>215</v>
-      </c>
-      <c r="H30" t="s">
-        <v>216</v>
-      </c>
-      <c r="I30" t="s">
-        <v>193</v>
-      </c>
-      <c r="J30" t="s">
-        <v>35</v>
-      </c>
-      <c r="K30" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
